--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -16,10 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-1_nenrei" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-2_koreika" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-3_shotoku" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-4_jukyusha" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-5_kyufuhi" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig9-1_hokenryo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-4_nintei" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-5_jukyusha" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-6_kyufuhi" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig3-1_kofukin" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig6-1_kpi" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig9-1_hokenryo" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,7 +562,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>6点</t>
+          <t>9点</t>
         </is>
       </c>
     </row>
@@ -576,12 +579,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.6_図表整理版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.7_図表追加版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>6点</t>
+          <t>9点</t>
         </is>
       </c>
     </row>
@@ -603,7 +606,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>6点（うち使用6点）</t>
+          <t>9点（うち使用9点）</t>
         </is>
       </c>
     </row>
@@ -712,24 +715,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>図2-4　サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
+          <t>図2-4　要介護認定者数と認定率の推移（令和6〜11年度）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>種類：円（ドーナツ）／差し込み先：2-3 要介護認定とサービス利用の状況　　資料：介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
+          <t>種類：縦3段（第1号被保険者数の棒・認定者数の棒・認定率の折れ線）／差し込み先：2-3 要介護認定とサービス利用の状況　　資料：介護保険事業状況報告（年報・令和6〜7年度）及び本計画の推計値</t>
         </is>
       </c>
     </row>
@@ -743,58 +749,177 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>第1号被保険者数（人）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>認定者数（人）</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>認定率（％）</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>区分</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>受給者数（人／月）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>居宅（介護予防）サービス</t>
+          <t>令和6年度</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>261.8</v>
+        <v>3270</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>554</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>地域密着型サービス</t>
+          <t>令和7年度</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>53.9</v>
+        <v>3285</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>560</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>実績</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>施設サービス</t>
+          <t>令和8年度</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>134.3</v>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>突合：素案 2-3 の表（サービス受給者数）の『延べ合計（重複あり）』450.0人と一致すること</t>
+        <v>3257</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>562</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>実績見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>3231</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>575</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>3203</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>571</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>3177</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>576</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>見込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>注記：※認定率は、第1号被保険者数に対する第1号被保険者の認定者数の割合。 　令和6年度から令和11年度までに、第1号被保険者数は93人（2.8％）減り、認定者数は22人（4.0％）増えます。 　認定率の1.2ポイントの上昇は、認定者の増加と被保険者の減少の双方によるものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>突合：素案 2-3 の認定率の表（7行5列）の第1号被保険者数・認定者数・認定率と一致すること</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A10:C10"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -816,14 +941,14 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>図2-5　サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+          <t>図2-5　サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>種類：縦棒／差し込み先：2-4 介護給付費の状況　　資料：介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+          <t>種類：円（ドーナツ）／差し込み先：2-3 要介護認定とサービス利用の状況　　資料：介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
         </is>
       </c>
     </row>
@@ -842,47 +967,44 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>給付費（億円）</t>
+          <t>受給者数（人／月）</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>居宅サービス
-（在宅・居宅介護支援を含む）</t>
+          <t>居宅（介護予防）サービス</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3.2268</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>地域密着型
-サービス</t>
+          <t>地域密着型サービス</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>1.8219</v>
+        <v>53.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>施設サービス
-（特養・老健）</t>
+          <t>施設サービス</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>4.9335</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>突合：素案 2-4 の給付費の表と一致し、計が9.98億円であること</t>
+          <t>突合：素案 2-3 の表（サービス受給者数）の『延べ合計（重複あり）』450.0人と一致すること</t>
         </is>
       </c>
     </row>
@@ -903,6 +1025,657 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>図2-6　サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>種類：縦棒／差し込み先：2-4 介護給付費の状況　　資料：介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。直したあとは data_zuhyo.py の同じ値を直し、build_plan_figures.py を実行し直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>給付費（億円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>居宅サービス
+（在宅・居宅介護支援を含む）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3.2268</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型
+サービス</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1.8219</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>施設サービス
+（特養・老健）</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>4.9335</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>突合：素案 2-4 の給付費の表と一致し、計が9.98億円であること</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>図3-1　保険者機能強化推進交付金等の得点の推移と指標群別の内訳</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>種類：積み上げ縦棒（3指標群）＋全国平均の折れ線／差し込み先：3-3 評価指標の達成状況　　資料：令和6・7・8年度 保険者機能強化推進交付金等に係る全国集計結果（市町村分）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。直したあとは data_zuhyo.py の同じ値を直し、build_plan_figures.py を実行し直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>年度</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>体制・取組指標群</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>活動指標群</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>成果指標群</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>全国平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>令和6年度</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>366</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>454</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>422.4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>令和7年度</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>366</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>565</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>353</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>528</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>455.1</v>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>注記：※満点は体制・取組指標群380点、活動指標群220点、成果指標群200点。 　成果指標群は推進・支援の双方で同じ5指標を評価するため、1つの指標の動きが2倍に効きます。 　令和7年度から令和8年度への37点の減少は、体制・取組指標群の13点（評価結果の活用16点が満点から0点）と成果指標群の30点が主なものです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>突合：素案 3-3 の表（得点454・565・528点、全国平均422.4・435.0・455.1点）及び3指標群の表（体制353点・活動95点・成果80点）と一致すること</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>図6-1　認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>種類：概念図（3層・指標の一覧つき）／差し込み先：6-3 重点施策とKPI　　資料：本計画 6-3 のKPIの表</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。直したあとは data_zuhyo.py の同じ値を直し、build_plan_figures.py を実行し直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>層</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>重点目標</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>指標</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>現状値の状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>プロセス（活動量）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>認知症サポーター養成講座 年間開催回数</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>プロセス（活動量）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1・3</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>認知症カフェ 年間開催回数</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>プロセス（活動量）</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>認知症の日・認知症月間の事業・行事の実施</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>プロセス（活動量）</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>重点目標2</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>認知症本人ミーティングの開催回数</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>プロセス（活動量）</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>重点目標3</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>庁内の部署横断的な検討の場の開催回数</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>認知症サポーター累計養成数</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>ステップアップ講座修了者数</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>チームオレンジ 活動状況</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>重点目標3</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>初期集中支援チーム 訪問件数</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>重点目標2</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>意思決定支援研修の実施と参加者数</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>アウトプット（成果物）</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>重点目標3</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>認知症対応力向上研修の受講者数</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>アウトカム（住民の変化）</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>重点目標3</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>認知症相談窓口を知っている人の割合</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>あり</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>アウトカム（住民の変化）</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>重点目標1</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>認知症観の変化（本人・家族への接し方）</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>アウトカム（住民の変化）</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>重点目標2</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>「思いを伝えられる相手がいる」人の割合</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>注記：※活動回数や成果物の数だけを追うのではなく、住民の変化（アウトカム）までの連なりで評価します。 　現状値が未確定の3指標は町のご確認を、目標値は第2回・第3回策定委員会のご協議をお願いします。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>突合：素案 6-3 のKPIの表（15行5列）の14指標と層・重点目標が一致すること</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1036,13 +1809,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1111,7 +1884,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>定義 6 ／ 画像 6</t>
+          <t>定義 9 ／ 画像 9</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1138,7 +1911,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>素案 6 ／ 定義 6</t>
+          <t>素案 9 ／ 定義 9</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1192,7 +1965,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>図2-1／図2-2／図2-3／図2-4／図2-5／図9-1</t>
+          <t>図2-1／図2-2／図2-3／図2-4／図2-5／図2-6／図3-1／図6-1／図9-1</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1263,17 +2036,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>08_図表 に使っていない画像が残っていないこと</t>
+          <t>本文の図の参照が、その図のある節と合っていること</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>08_図表/*.png - ZU の png</t>
+          <t>本文の段落の「図N-M」の節 == data_zuhyo.py の sec（表の中の参照は巻末の一覧と重なるため見ていない）</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>参照1件・食い違い なし</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1290,20 +2063,47 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
+          <t>08_図表 に使っていない画像が残っていないこと</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>08_図表/*.png - ZU の png</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
           <t>図の数値の正本が1か所であること</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>data_zuhyo.py のほかに図の数値を持つスクリプトが07_ソーススクリプト にないこと</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>data_zuhyo.py のみ</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -1324,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1557,12 +2357,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
+          <t>要介護認定者数と認定率の推移（令和6〜11年度）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>円（ドーナツ）</t>
+          <t>縦3段（第1号被保険者数の棒・認定者数の棒・認定率の折れ線）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1572,23 +2372,23 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
+          <t>介護保険事業状況報告（年報・令和6〜7年度）及び本計画の推計値</t>
         </is>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>fig2-4_jukyusha.png</t>
+          <t>fig2-4_nintei.png</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>D_fig2-4_jukyusha</t>
+          <t>D_fig2-4_nintei</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -1605,22 +2405,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>縦棒</t>
+          <t>円（ドーナツ）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2-4 介護給付費の状況</t>
+          <t>2-3 要介護認定とサービス利用の状況</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+          <t>介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
         </is>
       </c>
       <c r="F9" s="6" t="n">
@@ -1631,12 +2431,12 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>fig2-5_kyufuhi.png</t>
+          <t>fig2-5_jukyusha.png</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>D_fig2-5_kyufuhi</t>
+          <t>D_fig2-5_jukyusha</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -1648,46 +2448,190 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>図2-6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>縦棒</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>2-4 介護給付費の状況</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>fig2-6_kyufuhi.png</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>D_fig2-6_kyufuhi</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>図3-1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の得点の推移と指標群別の内訳</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>積み上げ縦棒（3指標群）＋全国平均の折れ線</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>3-3 評価指標の達成状況</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度 保険者機能強化推進交付金等に係る全国集計結果（市町村分）</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>fig3-1_kofukin.png</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>D_fig3-1_kofukin</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>概念図（3層・指標の一覧つき）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>本計画 6-3 のKPIの表</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>fig6-1_kpi.png</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>D_fig6-1_kpi</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>折れ線（実績＋3パターン）</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>本計画の算定値</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="G13" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>fig9-1_hokenryo.png</t>
         </is>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>D_fig9-1_hokenryo</t>
         </is>
       </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -1708,7 +2652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1848,17 +2792,17 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
+          <t>要介護認定者数と認定率の推移（令和6〜11年度）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>素案 2-3 の表（サービス受給者数）の『延べ合計（重複あり）』450.0人と一致すること</t>
+          <t>素案 2-3 の認定率の表（7行5列）の第1号被保険者数・認定者数・認定率と一致すること</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>261.8：あり／450.0：あり</t>
+          <t>3,270：あり／554：あり／16.9：あり／18.1：あり</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -1875,17 +2819,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>素案 2-4 の給付費の表と一致し、計が9.98億円であること</t>
+          <t>素案 2-3 の表（サービス受給者数）の『延べ合計（重複あり）』450.0人と一致すること</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>9.98：あり</t>
+          <t>261.8：あり／450.0：あり</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -1897,25 +2841,106 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>図2-6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>素案 2-4 の給付費の表と一致し、計が9.98億円であること</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>9.98：あり</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>図3-1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の得点の推移と指標群別の内訳</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>素案 3-3 の表（得点454・565・528点、全国平均422.4・435.0・455.1点）及び3指標群の表（体制353点・活動95点・成果80点）と一致すること</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>454点：あり／565点：あり／528点：あり／353点（92.9：あり／95点（43.2：あり／80点（40.0：あり</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>素案 6-3 のKPIの表（15行5列）の14指標と層・重点目標が一致すること</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>プロセス：あり／アウトプット：あり／アウトカム：あり／47.7：あり</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>素案 9-3 の3パターンの表（算定Ａ6,822円／Ｂ6,143円／Ｃ5,464円）と一致すること。保険料の検算（check_hokenryo_R8.9.30.py）と同じ値</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>6,822：あり／6,143：あり／5,464：あり</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -2265,7 +3290,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>要介護認定者数と認定率の推移（棒と折れ線）</t>
+          <t>要介護認定者数と認定率の推移（縦3段・被保険者数・認定者数・認定率）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -2285,7 +3310,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>未作成</t>
+          <t>作成済み（図2-4・令和8年10月1日）</t>
         </is>
       </c>
     </row>
@@ -2371,7 +3396,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>交付金_取りまとめ表_R8.9.29.xlsx</t>
+          <t>令和6〜8年度 全国集計結果（市町村分）の原典</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -2381,7 +3406,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>未作成</t>
+          <t>作成済み（図3-1・令和8年10月1日）</t>
         </is>
       </c>
     </row>
@@ -2413,7 +3438,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>未作成</t>
+          <t>作成済み（図6-1・令和8年10月1日）</t>
         </is>
       </c>
     </row>
@@ -2528,7 +3553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2710,12 +3735,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
+          <t>要介護認定者数と認定率の推移（令和6〜11年度）</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
+          <t>要介護認定者数と認定率の推移（令和6〜11年度）</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2730,7 +3755,7 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
+          <t>介護保険事業状況報告（年報・令和6〜7年度）及び本計画の推計値</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -2747,27 +3772,27 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+          <t>サービス受給者の区分別構成（令和7年度の月平均・延べ450.0人）</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2-4 介護給付費の状況</t>
+          <t>2-3 要介護認定とサービス利用の状況</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>2-4 介護給付費の状況</t>
+          <t>2-3 要介護認定とサービス利用の状況</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+          <t>介護保険事業状況報告（年報・令和7年度／様式1の6）</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -2779,35 +3804,146 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
+          <t>図2-6</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>サービス区分別の年間給付費（令和7年度実績・総額9.98億円）</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>2-4 介護給付費の状況</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2-4 介護給付費の状況</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告（年報・令和7年度／様式2給付費）</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>図3-1</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の得点の推移と指標群別の内訳</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の得点の推移と指標群別の内訳</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>3-3 評価指標の達成状況</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>3-3 評価指標の達成状況</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>令和6・7・8年度 保険者機能強化推進交付金等に係る全国集計結果（市町村分）</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>本計画 6-3 のKPIの表</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>本計画の算定値</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -20,9 +20,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-5_jukyusha" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig2-6_kyufuhi" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig3-1_kofukin" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig6-1_kpi" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig9-1_hokenryo" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig3-2_keikaku_jisseki" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig6-1_kpi" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D_fig9-1_hokenryo" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_自己点検" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +563,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>9点</t>
+          <t>10点</t>
         </is>
       </c>
     </row>
@@ -579,12 +580,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.7_図表追加版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.8_第9期対比版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>9点</t>
+          <t>10点</t>
         </is>
       </c>
     </row>
@@ -606,7 +607,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>9点（うち使用9点）</t>
+          <t>10点（うち使用10点）</t>
         </is>
       </c>
     </row>
@@ -1284,6 +1285,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>図3-2　第9期計画の計画値と実績値の対比（令和7年度・給付費）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>種類：横並びの棒（計画と実績）＋達成率／差し込み先：3-3 評価指標の達成状況　　資料：第9期計画書（令和6年3月）及び介護保険事業状況報告（年報・令和7年度／様式2 給付費）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>数値のセルのみを直してください。行・列の増減、見出しの書き換えは行わないでください。直したあとは data_zuhyo.py の同じ値を直し、build_plan_figures.py を実行し直します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>計画値（千円）</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>実績値（千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>居宅サービス
+（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>353651</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>322680</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>地域密着型サービス
+（介護予防を含む）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>179884</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>182190</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>施設サービス</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>477485</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>493350</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>総給付費</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1011020</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>998220</v>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>注記：※総給付費は計画を12,800千円（1.3％）下回りますが、区分の間で振れが相殺されています。 　居宅サービスが計画を8.8％下回る一方、施設サービスは3.3％上回っており、在宅から施設・居住系への移行が進んでいることが総額の一致に隠れています。 　第10期の見込量は、この移行が続くことを前提としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>突合：第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,220千円（9.98億円）と一致すること</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1670,7 +1803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1809,7 +1942,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1884,7 +2017,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>定義 9 ／ 画像 9</t>
+          <t>定義 10 ／ 画像 10</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1911,7 +2044,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>素案 9 ／ 定義 9</t>
+          <t>素案 10 ／ 定義 10</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1965,7 +2098,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>図2-1／図2-2／図2-3／図2-4／図2-5／図2-6／図3-1／図6-1／図9-1</t>
+          <t>図2-1／図2-2／図2-3／図2-4／図2-5／図2-6／図3-1／図3-2／図6-1／図9-1</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2124,7 +2257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2544,43 +2677,43 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>図6-1</t>
+          <t>図3-2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症施策のKPIの3層構造（14指標）</t>
+          <t>第9期計画の計画値と実績値の対比（令和7年度・給付費）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>概念図（3層・指標の一覧つき）</t>
+          <t>横並びの棒（計画と実績）＋達成率</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>6-3 重点施策とKPI</t>
+          <t>3-3 評価指標の達成状況</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>本計画 6-3 のKPIの表</t>
+          <t>第9期計画書（令和6年3月）及び介護保険事業状況報告（年報・令和7年度／様式2 給付費）</t>
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>fig6-1_kpi.png</t>
+          <t>fig3-2_keikaku_jisseki.png</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>D_fig6-1_kpi</t>
+          <t>D_fig3-2_keikaku_jisseki</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -2592,46 +2725,94 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>概念図（3層・指標の一覧つき）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>本計画 6-3 のKPIの表</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>fig6-1_kpi.png</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>D_fig6-1_kpi</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>折れ線（実績＋3パターン）</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>本計画の算定値</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="G14" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>fig9-1_hokenryo.png</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>D_fig9-1_hokenryo</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -2652,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2895,22 +3076,22 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>図6-1</t>
+          <t>図3-2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症施策のKPIの3層構造（14指標）</t>
+          <t>第9期計画の計画値と実績値の対比（令和7年度・給付費）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>素案 6-3 のKPIの表（15行5列）の14指標と層・重点目標が一致すること</t>
+          <t>第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,220千円（9.98億円）と一致すること</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>プロセス：あり／アウトプット：あり／アウトカム：あり／47.7：あり</t>
+          <t>998,220：あり／1,011,020：あり</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2922,25 +3103,52 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>素案 6-3 のKPIの表（15行5列）の14指標と層・重点目標が一致すること</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>プロセス：あり／アウトプット：あり／アウトカム：あり／47.7：あり</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>素案 9-3 の3パターンの表（算定Ａ6,822円／Ｂ6,143円／Ｃ5,464円）と一致すること。保険料の検算（check_hokenryo_R8.9.30.py）と同じ値</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>6,822：あり／6,143：あり／5,464：あり</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
@@ -3364,17 +3572,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>町の第9期実績一覧（確認事項No.133）</t>
+          <t>第9期計画書の計画値と年報の実績値（当方の手元にある）</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>町のご記入後</t>
+          <t>受託者の作業のみで作れる</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>未作成</t>
+          <t>作成済み（図3-2・令和8年10月2日）</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3878,32 +4086,32 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>図6-1</t>
+          <t>図3-2</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>認知症施策のKPIの3層構造（14指標）</t>
+          <t>第9期計画の計画値と実績値の対比（令和7年度・給付費）</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>認知症施策のKPIの3層構造（14指標）</t>
+          <t>第9期計画の計画値と実績値の対比（令和7年度・給付費）</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>6-3 重点施策とKPI</t>
+          <t>3-3 評価指標の達成状況</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>6-3 重点施策とKPI</t>
+          <t>3-3 評価指標の達成状況</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>本計画 6-3 のKPIの表</t>
+          <t>第9期計画書（令和6年3月）及び介護保険事業状況報告（年報・令和7年度／様式2 給付費）</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -3915,35 +4123,72 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>図6-1</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>認知症施策のKPIの3層構造（14指標）</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>6-3 重点施策とKPI</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>本計画 6-3 のKPIの表</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>図9-1</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>介護保険料月額基準額の推移と第10期の3パターン</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>9-3 介護保険料の算定</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>本計画の算定値</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>一致</t>
         </is>

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -1948,7 +1948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2196,17 +2196,17 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>08_図表 に使っていない画像が残っていないこと</t>
+          <t>未作成の図に、作図の枠が用意されていること</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>08_図表/*.png - ZU の png</t>
+          <t>KOUHO の未作成 ⊆ WAKU の候補番号</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>未作成 4件・枠 4件・枠なし なし</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2223,20 +2223,47 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>08_図表 に使っていない画像が残っていないこと</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>08_図表/*.png - ZU の png</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>なし</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
           <t>図の数値の正本が1か所であること</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>data_zuhyo.py のほかに図の数値を持つスクリプトが07_ソーススクリプト にないこと</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>data_zuhyo.py のみ</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>適合</t>
         </is>

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.8_第9期対比版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.9_事業内容版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.9_事業内容版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.10_制度改正補完版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.10_制度改正補完版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.15_実績是正版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -781,13 +781,13 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>3270</v>
+        <v>3261</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>3285</v>
+        <v>3240</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
@@ -823,13 +823,13 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>3257</v>
+        <v>3229</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>562</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>注記：※認定率は、第1号被保険者数に対する第1号被保険者の認定者数の割合。 　令和6年度から令和11年度までに、第1号被保険者数は93人（2.8％）減り、認定者数は22人（4.0％）増えます。 　認定率の1.2ポイントの上昇は、認定者の増加と被保険者の減少の双方によるものです。</t>
+          <t>注記：※認定率は、第1号被保険者数に対する第1号被保険者の認定者数の割合。 　令和6年度から令和11年度までに、第1号被保険者数は84人（2.6％）減り、認定者数は19人（3.4％）増えます。 　認定率の1.0ポイントの上昇は、認定者の増加と被保険者の減少の双方によるものです。</t>
         </is>
       </c>
     </row>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>参照1件・食い違い なし</t>
+          <t>参照2件・食い違い なし</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>3,270：あり／554：あり／16.9：あり／18.1：あり</t>
+          <t>3,261：あり／557：あり／17.1：あり／18.1：あり</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.15_実績是正版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.17_中長期補完版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.17_中長期補完版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.18_範囲明記版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.18_範囲明記版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.19_認知症推計版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.19_認知症推計版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.20_事業所確定版.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -1342,7 +1342,7 @@
         <v>353651</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>322680</v>
+        <v>322676</v>
       </c>
     </row>
     <row r="7">
@@ -1356,7 +1356,7 @@
         <v>179884</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>182190</v>
+        <v>182194</v>
       </c>
     </row>
     <row r="8">
@@ -1369,7 +1369,7 @@
         <v>477485</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>493350</v>
+        <v>493352</v>
       </c>
     </row>
     <row r="9">
@@ -1382,20 +1382,20 @@
         <v>1011020</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>998220</v>
+        <v>998222</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>注記：※総給付費は計画を12,800千円（1.3％）下回りますが、区分の間で振れが相殺されています。 　居宅サービスが計画を8.8％下回る一方、施設サービスは3.3％上回っており、在宅から施設・居住系への移行が進んでいることが総額の一致に隠れています。 　第10期の見込量は、この移行が続くことを前提としています。</t>
+          <t>注記：※総給付費は計画を12,798千円（1.3％）下回りますが、区分の間で振れが相殺されています。 　居宅サービスが計画を8.8％下回る一方、施設サービスは3.3％上回っており、在宅から施設・居住系への移行が進んでいることが総額の一致に隠れています。 　第10期の見込量は、この移行が続くことを前提としています。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>突合：第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,220千円（9.98億円）と一致すること</t>
+          <t>突合：第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,222千円（9.98億円）と一致すること</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,220千円（9.98億円）と一致すること</t>
+          <t>第9期_計画値実績対比表（08_区分別のまとめ）と一致し、実績の合計が素案 2-4 の総額998,222千円（9.98億円）と一致すること</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>998,220：あり／1,011,020：あり</t>
+          <t>998,222：あり／1,011,020：あり</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.20_事業所確定版.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.33_協議用.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.33_協議用.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.34_協議用.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.34_協議用.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.35_協議用.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
+++ b/kawasaki_project/05_試算・管理シート/川崎町_図表データ管理台帳_R8.9.30.xlsx
@@ -580,7 +580,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>素案（川崎町_計画書素案_v2.35_協議用.docx）の本文に画像として置いているもの</t>
+          <t>素案（川崎町_計画書素案_v2.36_協議用.docx）の本文に画像として置いているもの</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
